--- a/www/download/COUNTRY.BEL.rpO2.xlsx
+++ b/www/download/COUNTRY.BEL.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.7299483476926</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.767200650712243</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.885559181066731</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.89852905874464</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.938262384526172</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1.08271977599631</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1.1165698681726</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1.05752964628676</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.884017016719317</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.803923186934283</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.803793926163139</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.796431999331189</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.729660720440948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.679902075880751</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.71694868628827</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.867</t>
+          <t>-0.866109915067833</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>-0.845592143669344</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.904</t>
+          <t>-0.801186512598691</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>-0.811411456236959</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>-0.850149559972997</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>-0.893729807419998</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.165</t>
+          <t>-0.897669213796675</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.159</t>
+          <t>-0.907769503463628</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>-0.913891334495633</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>-0.919832584184776</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.258</t>
+          <t>-0.933540735012234</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.308</t>
+          <t>-0.930093833575639</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>-0.913377930238943</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>-0.91030363396788</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.438</t>
+          <t>-0.881460657137076</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>-0.796173622810814</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>-0.766144989557936</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.198</t>
+          <t>-0.700261252337422</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.268</t>
+          <t>-0.716450294495929</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.323</t>
+          <t>-0.773039880527274</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>-0.841797242063861</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.848717710911928</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.864433487845195</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>-0.877293317592664</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.507</t>
+          <t>-0.879701185144381</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.563</t>
+          <t>-0.899832484944958</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>-0.893385461833469</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.672</t>
+          <t>-0.870619835838988</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>-0.86990003129843</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>-0.828176802108588</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5537.162</t>
+          <t>-0.788430714177001</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5534.511</t>
+          <t>-0.756954618219614</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5603.697</t>
+          <t>-0.687977726391873</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5685.502</t>
+          <t>-0.704022115952161</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5787.52</t>
+          <t>-0.765667467466919</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5961.599</t>
+          <t>-0.833587524507574</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6030.447</t>
+          <t>-0.84106885004181</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5990.895</t>
+          <t>-0.858275770773434</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5992.714</t>
+          <t>-0.891055848331974</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6057.565</t>
+          <t>-0.873176125269277</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6122.792</t>
+          <t>-0.894419328004336</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6209.157</t>
+          <t>-0.88722582245579</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6331.202</t>
+          <t>-0.856595485539716</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6412.834</t>
+          <t>-0.857595446299328</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6293.109</t>
+          <t>-0.811850720134115</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4595.1</t>
+          <t>289659592271.263</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4585.6</t>
+          <t>259257188523.978</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4644.6</t>
+          <t>204985460788.068</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4729.2</t>
+          <t>220130545239.293</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4818.4</t>
+          <t>290646147496.291</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4982.1</t>
+          <t>452918593892.127</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5057.8</t>
+          <t>461788592270.518</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5033.1</t>
+          <t>449888317343.868</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5028.4</t>
+          <t>524409572737.706</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5082.2</t>
+          <t>581650389358.505</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>726273368904.091</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5218.2</t>
+          <t>770104670567.067</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5322.6</t>
+          <t>689300461983.721</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5400.1</t>
+          <t>677656968421.879</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5284.4</t>
+          <t>419177938008.351</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>106022267358.486</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>93279951884.4703</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>74742936000.0389</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>79012474823.7041</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>102863901750.89</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>149843325530.296</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>157777497852.002</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>174773039686.628</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>198059037885.596</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>198023051002.279</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>244024098852.708</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>234852624604.991</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>196012377786.7</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>200553711489.969</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>149712731666.511</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>22079940.0155612</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>20768129.4450979</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>18049783.483807</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>18665944.1154791</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>25139835.5600457</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>38472858.0795316</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>40063073.0248058</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>38576448.4628996</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>37770938.3493561</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>34303075.0113113</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>39778809.1094237</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>36468465.8472715</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>28002164.2261778</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>24884715.8377169</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>56.94</t>
+          <t>19309754.0927181</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>5036.57208691442</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>5254.26008620335</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>5269.66227376099</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>5138.72388796218</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>4882.84668751555</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>3876.31438703227</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>3669.58239685835</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>3776.29126574695</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>3809.06293815707</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>4113.96580465159</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>3984.87289531886</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>4283.12706154782</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>5561.72180935347</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>6319.45609393754</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>7198.60626791517</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>121436.343833867</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>112863.069983447</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>87903.3448988941</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>92849.2989726976</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>114157.875687926</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>140302.439395547</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>136065.511089189</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>139297.248504199</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>166008.824561457</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>198888.637080127</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>240063.02607829</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>269767.41733582</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>307728.194870485</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>338516.342278976</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>241836.914905597</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>-0.808187904307257</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>-0.780252580050876</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>-0.718637427064838</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>-0.734028833797128</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>49.99</t>
+          <t>-0.788411611881746</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>-0.851561244367653</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>-0.858213625632731</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>-0.873059865850377</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>-0.889009216256148</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>-0.888275780651813</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>-0.907155794902085</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>-0.901571787086369</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>59.38</t>
+          <t>-0.878943823434686</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>-0.879314216252301</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>-0.84118498176207</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>62182.6622563998</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>61459.7852163008</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>54898.5796373611</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>57959.8632996363</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>58927.178840252</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>54204.1396966795</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>56140.9223292916</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>59000.2544874741</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>73014.0204700645</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>85672.9263729353</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>90857.4369084485</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>96451.1149533829</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>109746.04455259</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>124144.43780264</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>119286.866911306</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7299483476926</t>
+          <t>33456.8876603736</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.767200650712243</t>
+          <t>29396.372497256</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885559181066731</t>
+          <t>23368.3258756178</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89852905874464</t>
+          <t>24179.1258219847</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262384526172</t>
+          <t>30959.1003092451</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977599631</t>
+          <t>43979.7908571073</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1165698681726</t>
+          <t>45474.0780536401</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964628676</t>
+          <t>50368.423374043</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017016719317</t>
+          <t>57050.7334841547</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923186934283</t>
+          <t>56464.1505792829</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793926163139</t>
+          <t>68480.4232269132</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999331189</t>
+          <t>65066.0418083062</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660720440948</t>
+          <t>53374.2449550773</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902075880751</t>
+          <t>53647.8416713016</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694868628827</t>
+          <t>40279.0537854545</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>267828877644.119</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>244186846402.803</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>198400155567.915</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>205328785698.969</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>275928500772.567</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>370447201079.358</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>397207274691.973</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>455430861622.918</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>514641598760.754</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>531642123219.944</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>608795905729.817</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>591587943661.644</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>502107476045.816</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>450188696162.037</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>330516929917.867</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>241117403645.363</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>211527927876.44</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>170705393499.463</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>175977700671.789</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>234498976058.487</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>330242401646.254</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>335210892155.937</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>373875755463.717</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>442840477464.891</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>442862968170.511</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>524377357149.242</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>505455602385.855</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>422240734761.193</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>369289542400.173</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>264709705478.185</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>26711473998.7561</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>32658918526.3626</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>27694762068.452</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>29351085027.1801</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>41429524714.0798</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>40204799433.1037</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>61996382536.036</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>81555106159.2016</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>71801121295.8625</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>88779155049.4335</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>84418548580.5748</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>86132341275.789</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.477</t>
+          <t>79866741284.6231</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>80899153761.8638</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>65807224439.6815</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>6417.43573749292</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>6459.77701213539</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>6574.97229355113</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>6430.95029263923</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>6550.58613202451</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>6528.3054277999</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>6447.60465491984</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>6393.77442000603</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>6332.10562256797</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>6308.41314462888</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>6358.01045927154</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.849</t>
+          <t>6404.33421655518</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>6461.28202132214</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>6474.53181847351</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>6396.91866154351</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>6220.01887449003</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>6254.40840247272</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>6362.08952473822</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>6228.89576567248</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>6353.75601850156</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>6347.13977755965</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>6290.19903808325</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>6233.65308949959</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>6182.86779061643</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>6164.08579795886</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>6214.51196849118</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>6265.89145114591</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>6326.60631347547</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>6356.22721086514</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>6263.29083689581</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-86.61</t>
+          <t>177513.724249902</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-84.56</t>
+          <t>173479.376536638</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-80.12</t>
+          <t>164690.676764728</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-81.14</t>
+          <t>162774.108847925</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-85.01</t>
+          <t>160458.565785168</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-89.37</t>
+          <t>161850.185048457</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-89.77</t>
+          <t>162421.29888976</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-90.78</t>
+          <t>170547.540206467</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-91.39</t>
+          <t>200681.067021766</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-91.98</t>
+          <t>238705.533185001</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-93.35</t>
+          <t>247065.800135292</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-93.01</t>
+          <t>273343.026589669</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-91.34</t>
+          <t>324688.835284459</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-91.03</t>
+          <t>375094.150818069</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-88.15</t>
+          <t>301037.714775515</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-79.62</t>
+          <t>158615328440.91</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-76.61</t>
+          <t>141151115740.313</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-70.03</t>
+          <t>113376386961.208</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-71.65</t>
+          <t>120479375232.668</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-77.3</t>
+          <t>157277539257.161</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-84.18</t>
+          <t>258249484748.005</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-84.87</t>
+          <t>257407482784.048</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-86.44</t>
+          <t>249013080273.635</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-87.73</t>
+          <t>301719680541.523</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-87.97</t>
+          <t>334339780385.153</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-89.98</t>
+          <t>426365212687.664</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-89.34</t>
+          <t>454991808680.528</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-87.06</t>
+          <t>414779445159.62</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-86.99</t>
+          <t>421947063376.335</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-82.82</t>
+          <t>242736151527.366</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-78.84</t>
+          <t>155354.044170616</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-75.7</t>
+          <t>152499.637195941</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-68.8</t>
+          <t>143810.096571035</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-70.4</t>
+          <t>144436.832500273</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-76.57</t>
+          <t>141951.659026442</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-83.36</t>
+          <t>147219.957489576</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-84.11</t>
+          <t>146747.689357156</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-85.83</t>
+          <t>148688.660044613</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-89.11</t>
+          <t>175032.757146186</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-87.32</t>
+          <t>210429.495545863</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>221153.776608734</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-88.72</t>
+          <t>246146.915333527</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-85.66</t>
+          <t>292889.792187384</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-85.76</t>
+          <t>354991.525157902</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-81.19</t>
+          <t>275136.130911899</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>24053.933</t>
+          <t>334689341136.079</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>24252.107</t>
+          <t>302032022206.155</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24838.577</t>
+          <t>240065528484.425</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>24745.895</t>
+          <t>256957818028.066</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>25590.42</t>
+          <t>341998129697.476</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26080.124</t>
+          <t>525873886267.591</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26201.39</t>
+          <t>536552792106.74</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25925.427</t>
+          <t>546693510612.638</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25723.401</t>
+          <t>638710949142.372</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25881.4</t>
+          <t>686406411304.055</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>26461.448</t>
+          <t>862415405581.645</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>26996.562</t>
+          <t>878000509603.866</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>27698.566</t>
+          <t>770178777237.179</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>28284.533</t>
+          <t>791078228744.669</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>27793.701</t>
+          <t>489282483561.547</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20336.353</t>
+          <t>22159.6800792858</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20498.029</t>
+          <t>20979.7393406965</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21029.865</t>
+          <t>20880.5801936927</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>21015.04</t>
+          <t>18337.2763476516</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21764.807</t>
+          <t>18506.9067587257</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22242.557</t>
+          <t>14630.227558881</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>22370.699</t>
+          <t>15673.6095326039</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22185.713</t>
+          <t>21858.880161855</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21982.728</t>
+          <t>25648.3098755797</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22123.971</t>
+          <t>28276.0376391382</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22656.223</t>
+          <t>25912.0235265583</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>23116.124</t>
+          <t>27196.1112561413</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>23728.509</t>
+          <t>31799.0430970755</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>24203.982</t>
+          <t>20102.6256601672</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>23776.63</t>
+          <t>25901.5838636155</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>289659.592</t>
+          <t>-176074012695.169</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>259257.189</t>
+          <t>-160880906465.842</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>204985.461</t>
+          <t>-126689141523.217</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>220130.545</t>
+          <t>-136478442795.397</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>290646.147</t>
+          <t>-184720590440.315</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>452918.594</t>
+          <t>-267624401519.586</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>461788.592</t>
+          <t>-279145309322.692</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>449888.317</t>
+          <t>-297680430339.002</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>524409.573</t>
+          <t>-336991268600.849</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>581650.389</t>
+          <t>-352066630918.902</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>726273.369</t>
+          <t>-436050192893.98</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>770104.671</t>
+          <t>-423008700923.338</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>689300.462</t>
+          <t>-355399332077.559</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>677656.968</t>
+          <t>-369131165368.335</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>419177.938</t>
+          <t>-246546332034.18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>117847.10491</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112987.65254</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>102377.91139</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>103401.21995</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>100904.07742</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>91991.6699</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>90815.81233</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>97443.41446</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>118505.86321</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>135255.33413</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>137671.1065</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>145710.11847</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>166173.53261</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>183373.46257</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>168451.19134</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12013.631</t>
+          <t>0.0252644913529974</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12069.534</t>
+          <t>0.0220593624470564</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12288.544</t>
+          <t>0.0239556813852598</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12183.076</t>
+          <t>0.0227886677505537</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12431.736</t>
+          <t>0.0175323313582896</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12513.359</t>
+          <t>0.0195937006024185</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12454.084</t>
+          <t>0.0133053958446252</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>12196.288</t>
+          <t>0.0156247310148504</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12032.548</t>
+          <t>0.0171332513347472</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>12031.305</t>
+          <t>0.0199367728433169</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12055.614</t>
+          <t>0.0199199713540407</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>12227.037</t>
+          <t>0.0199328828946529</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>12458.064</t>
+          <t>0.020869943253171</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>12650.566</t>
+          <t>0.0148154969255332</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12477.404</t>
+          <t>0.00752873550948811</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>145787.436978897</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>141086.82183962</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>127201.43659137</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>129745.94339465</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>130798.806343329</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>118625.892780869</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>121459.216405026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>133173.760639047</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>162243.029399309</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>183289.402962845</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>189538.754053939</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>200242.206394935</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>229984.011665091</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>260066.435398422</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>249276.082989467</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>106022.267</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>93279.952</t>
+          <t>166925.935825279</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>74742.936</t>
+          <t>150238.850509246</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>79012.475</t>
+          <t>152780.082432811</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>102863.902</t>
+          <t>153789.385768597</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>149843.326</t>
+          <t>139092.734411134</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>157777.498</t>
+          <t>142257.524134406</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>174773.04</t>
+          <t>155622.068038809</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>198059.038</t>
+          <t>189850.98373018</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>198023.051</t>
+          <t>214418.395190387</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>244024.099</t>
+          <t>221372.722061265</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>234852.625</t>
+          <t>233856.294647683</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>196012.378</t>
+          <t>268463.02295684</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>200553.711</t>
+          <t>304290.862609071</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>149712.732</t>
+          <t>291661.720887746</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-80.82</t>
+          <t>856723.160922217</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-78.03</t>
+          <t>843663.633211832</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-71.86</t>
+          <t>758561.906929261</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-73.4</t>
+          <t>779376.667471995</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-78.84</t>
+          <t>783058.218019589</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-85.16</t>
+          <t>715560.663943996</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-85.82</t>
+          <t>718025.400210937</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-87.31</t>
+          <t>774142.33641661</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-88.9</t>
+          <t>959426.798719664</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-88.83</t>
+          <t>1117434.49111651</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-90.72</t>
+          <t>1178579.94687948</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-90.16</t>
+          <t>1273352.67021226</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-87.89</t>
+          <t>1476781.63982967</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>1691948.83062529</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-84.12</t>
+          <t>1618600.58645843</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20.768</t>
+          <t>174972.110251644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>180485.867200163</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>18.666</t>
+          <t>183477.087066379</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>192019.397675357</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>38.473</t>
+          <t>197541.591392764</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>40.063</t>
+          <t>204298.36309091</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>38.576</t>
+          <t>205733.840799611</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>37.771</t>
+          <t>203974.716814737</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>34.303</t>
+          <t>204434.566816834</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>39.779</t>
+          <t>206651.714656127</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>36.468</t>
+          <t>211469.592023376</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>28.002</t>
+          <t>218010.089434338</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>24.885</t>
+          <t>225203.004860929</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>222432.517407521</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>145787.436978897</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>148108.679842194</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>153161.249872419</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>156268.66213584</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>164173.134836257</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>169757.696272514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>176199.126719409</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>177163.450461632</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>175487.571196141</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>176234.781917319</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>177815.765467754</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>181904.498785449</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>187670.198415123</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>193154.220820428</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>190343.137159385</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>83827.3371474317</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80070.467084721</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>73070.4469907535</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75720.8192271894</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>72656.0149914032</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>68224.621108866</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>65694.5345055935</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>71096.0202611915</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>89452.1209498204</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107950.963989613</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>114334.715688735</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>121832.704612317</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140566.39357316</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>149211.500500929</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>131472.882622254</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20336353292.1275</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20498028759.5908</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>21029864781.6991</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>21015040073.4356</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>21764807167.0252</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>22242556781.5299</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>22370699377.175</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>22185713103.558</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>21982727842.4757</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>22123970786.1759</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>22656223482.7146</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>23116124137.9451</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>23728509014.3337</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>24203981854.6768</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>23776630210.0671</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>24053932591.0503</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>24252106530.245</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>24838577266.3648</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>24745895484.2415</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>25590419508.897</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>26080124418.9822</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>26201390069.4022</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>25925426581.962</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>25723401007.8499</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>25881399767.4076</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>26461447892.4432</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>26996561987.8049</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>27698565713.8775</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>28284533020.5126</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>27793701018.4628</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>12013630936.8496</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>12069534329.7203</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>12288544316.7929</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>12183076273.1329</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>12431736049.6532</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>12513359491.2691</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12454083887.2469</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>12196287734.2551</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>12032547505.8736</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>12031304790.5252</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>12055613517.9017</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>12227036857.5464</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12458063565.5624</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>12650566379.9347</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>12477404175.8537</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3867180</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3877602</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3904154</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3972758</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4027605</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4108957</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4165431</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4158946</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4160432</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4198741</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4258009</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4308495</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4378108</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4449893.32227832</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4437555.55062773</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3168922</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3173179</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3198472</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3267797</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3322574</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3407095</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3469614</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3469893</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3471630</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3507058</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3563414</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3609450</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3672415</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3738337</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3716888</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5537161563.7762</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5534510709.31955</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5603696769.77835</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5685501816.20563</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5787519958.512</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5961599139.40131</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6030447322.11266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5990894959.81838</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5992714488.46031</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6057565469.25483</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6122792221.14095</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6209157272.36833</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6331201978.02203</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6412833763.09854</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6293109306.44956</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4595100000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4585600000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4644600000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4729200000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4818400000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4982100000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5057800000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5033100000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5028400000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5082200000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5.144e+09</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5218200000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5322600000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5400100000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5284400000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.165843288808873</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.16971428572366</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.172865910570744</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.175109402495878</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.177047456686726</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.178402507200353</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.179995020415257</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.180132552108903</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.166563098005101</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.191720799927915</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.195351821530963</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.198012537488662</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.203713298460781</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.223534403901085</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.225223664202211</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.445526173294926</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.457877195974051</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.467406095339612</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.475852796445434</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.480561974817937</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.49979139344762</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.511218651781974</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.519639347364957</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.502523407533596</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.545194857547996</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.554528964233844</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.561598394579096</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.573414145424168</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.564980568882856</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.569376291647569</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.388630537896201</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.372408518302289</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.359727994089643</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.349037801058688</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.342390568495337</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.321806099352027</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.308786327802769</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.30022810052614</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.330913494461304</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.263084342524089</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.250119214235193</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.240389067932242</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.222872556115051</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.21148502721606</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.20540004415022</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.115659741544566</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.119230744064524</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.122177648215674</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.124250611989703</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.125694294726123</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.127273408489188</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.129670759247346</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.13126738276117</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.132653441270207</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.139381275156615</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.141954420237789</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.142477529378672</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.148554207443421</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.170539732797016</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.172267612866357</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.458345020135554</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.472067124700069</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.482795676750388</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.492247004959802</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.499927097718679</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.517127740576561</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.529645758851097</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.538480827969708</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.54663524183637</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.567256667411875</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.578512912924773</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.587281382681211</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.593824328538605</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.587424750347006</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.592746490029178</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.42599523831988</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.408702131235407</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.395026675033938</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.383502383050495</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.374378607555198</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.355598850934251</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.340683481901557</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.330251789269123</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.320711316893423</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.29336205743151</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.279532666837438</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.270241087940117</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.257621464017973</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.242035516855977</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.234985897104465</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>565662.49026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>551434.48693</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>507003.8431</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>522685.70802</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>523220.59463</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>492505.09565</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>496622.57662</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>526176.36293</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>637060.47889</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>745492.87068</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>783492.97772</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>848835.80683</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>978761.05105</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1103399.79032</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>972907.41524</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>256265.39088</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>246996.40291</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>223309.2975</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>228500.90166</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226445.40076</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>207317.35552</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>207952.05864</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>226718.0883</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>279303.10468</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>322369.35918</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>335707.43775</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>355688.99926</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>409029.41653</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>453502.36311</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>423134.60351</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>625363.65605692</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>642240.787117299</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>660940.924905751</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>680429.847094052</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>700182.100497513</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>721449.55282383</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>742284.419267126</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>759731.713392547</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>776340.031278286</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>796201.566599279</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>818671.25242229</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>841202.487809592</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>866528.736035931</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>892642.539159863</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>914298.655567405</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
